--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J284-PrestationsDirects-SERAFIN.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J284-PrestationsDirects-SERAFIN.xlsx
@@ -330,7 +330,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-SERAFINPH/</t>
+    <t>https://smt.esante.gouv.fr/terminologie-SERAFINPH</t>
   </si>
 </sst>
 </file>
